--- a/data/gravel/Lee Cougan Innova Supergravel 2025.xlsx
+++ b/data/gravel/Lee Cougan Innova Supergravel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B869ACC2-0C0C-9F45-B93F-A33D1AB8AF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD44497-9E37-F145-A9F9-84C92479E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8080" yWindow="3320" windowWidth="20720" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -390,6 +390,24 @@
   </si>
   <si>
     <t>Axle height</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -734,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1362,162 +1380,192 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>70</v>
+      </c>
+      <c r="B56" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>80</v>
-      </c>
-      <c r="B57" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>73</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>90</v>
-      </c>
-      <c r="B64" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="B69" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>96</v>
-      </c>
-      <c r="B70">
-        <v>3299</v>
+        <v>90</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>97</v>
-      </c>
-      <c r="B71">
-        <v>5899</v>
+        <v>91</v>
+      </c>
+      <c r="B71" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+      <c r="B77">
+        <v>5899</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>99</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>112</v>
       </c>
     </row>

--- a/data/gravel/Lee Cougan Innova Supergravel 2025.xlsx
+++ b/data/gravel/Lee Cougan Innova Supergravel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD44497-9E37-F145-A9F9-84C92479E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C24124-5B34-CC4E-B1DE-510F3F46E6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8080" yWindow="3320" windowWidth="20720" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="3640" windowWidth="24620" windowHeight="14240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>top_tube_h at actual height of seat tube not virtual height</t>
   </si>
 </sst>
 </file>
@@ -861,6 +864,9 @@
       <c r="E10">
         <v>625</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">

--- a/data/gravel/Lee Cougan Innova Supergravel 2025.xlsx
+++ b/data/gravel/Lee Cougan Innova Supergravel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C24124-5B34-CC4E-B1DE-510F3F46E6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1918FA6-6A0F-3740-A8CC-B48EEFDAAACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="3640" windowWidth="24620" windowHeight="14240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -167,9 +167,6 @@
     <t>axle_crown</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>handlebar_width</t>
   </si>
   <si>
@@ -215,18 +212,12 @@
     <t>tire_width_max_700c</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>tire_width_max_650b</t>
   </si>
   <si>
     <t>suspension_corrected</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>fork_suspension</t>
   </si>
   <si>
@@ -239,9 +230,6 @@
     <t>rear_axle</t>
   </si>
   <si>
-    <t>142</t>
-  </si>
-  <si>
     <t>front_axle</t>
   </si>
   <si>
@@ -338,9 +326,6 @@
     <t>rider_max</t>
   </si>
   <si>
-    <t>a8:e33</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -411,6 +396,18 @@
   </si>
   <si>
     <t>top_tube_h at actual height of seat tube not virtual height</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:e34</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -755,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -798,12 +795,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -811,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -865,7 +862,7 @@
         <v>625</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -936,13 +933,13 @@
         <v>73</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G14">
         <v>428</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1001,7 +998,7 @@
         <v>459.2</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G16" s="1">
         <v>70.861999999999995</v>
@@ -1055,7 +1052,7 @@
         <v>630.5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G18" s="1">
         <v>2.25</v>
@@ -1081,7 +1078,7 @@
         <v>310</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G19">
         <f>622 + (G18*25.4)*2</f>
@@ -1109,7 +1106,7 @@
         <v>100</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G20">
         <f>G19/2</f>
@@ -1162,7 +1159,7 @@
         <v>58</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G22">
         <f>G20-G21</f>
@@ -1202,157 +1199,163 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>44</v>
+      <c r="A25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>45</v>
+      <c r="A26" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29">
-        <v>700</v>
-      </c>
-      <c r="D29">
-        <v>700</v>
-      </c>
-      <c r="E29">
-        <v>700</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31">
         <v>50</v>
       </c>
-      <c r="C31">
-        <v>55</v>
-      </c>
       <c r="D31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E31">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32">
+        <v>55</v>
+      </c>
+      <c r="D32">
+        <v>55</v>
+      </c>
+      <c r="E32">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
         <v>52</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" t="s">
-        <v>55</v>
+      <c r="A39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="B43">
+        <v>2.4</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B45">
         <v>100</v>
@@ -1360,219 +1363,230 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="B48">
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>64</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B60" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="B64" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="B66" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>81</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>96</v>
-      </c>
-      <c r="B76">
-        <v>3299</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B77">
-        <v>5899</v>
+        <v>3299</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>93</v>
+      </c>
+      <c r="B78">
+        <v>5899</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>99</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>109</v>
+      <c r="A80" t="s">
+        <v>95</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
